--- a/artfynd/A 71719-2021 artfynd.xlsx
+++ b/artfynd/A 71719-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71719-2021 artfynd.xlsx
+++ b/artfynd/A 71719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114123724</v>
+        <v>79395106</v>
       </c>
       <c r="B2" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>90</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Bottnisk malört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Artemisia campestris subsp. bottnica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Lundstr. ex Kindb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Piteå Kommun, Nb</t>
+          <t>Korsningen Munksundsvägen, väg BD506, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>804806</v>
+        <v>804706</v>
       </c>
       <c r="R2" t="n">
-        <v>7253425</v>
+        <v>7253870</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +760,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Tor Hansson Frank</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114123681</v>
+        <v>114123724</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>804738</v>
+        <v>804806</v>
       </c>
       <c r="R3" t="n">
-        <v>7253724</v>
+        <v>7253425</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,12 +876,7 @@
         <v>114123705</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,12 +973,7 @@
         <v>114123700</v>
       </c>
       <c r="B5" t="n">
-        <v>91648</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,12 +990,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,53 +1067,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119274944</v>
+        <v>114123681</v>
       </c>
       <c r="B6" t="n">
-        <v>96868</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormknabben, Ormknabben, Nb</t>
+          <t>Piteå Kommun, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>804828</v>
+        <v>804738</v>
       </c>
       <c r="R6" t="n">
-        <v>7253403</v>
+        <v>7253724</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,15 +1152,122 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119274944</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ormknabben, Ormknabben, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>804828</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7253403</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Jacob Björnberg</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Jacob Björnberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71719-2021 artfynd.xlsx
+++ b/artfynd/A 71719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79395106</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114123724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114123705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114123700</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114123681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119274944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>